--- a/docs/算定テスト_10世帯.xlsx
+++ b/docs/算定テスト_10世帯.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="医療判定" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パラメータ" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教育費(段階別)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="就労収入(60歳まで)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -693,7 +694,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>2026-09-23再構築（60dbe72追随・検算自体は8/23に人が実施済み）。教育費を段階別モデル（対応コミット 60dbe72・2026-08-23）に追随。GT-02・GT-06 の教育費／必要額／提示レンジを「教育費(段階別)」シートの式から引き直した。他8世帯は不変。 2026-10-17：遺族年金の受給要件を現行制度に合わせた（QA指摘）。GT-04 の遺族厚生年金を5年→算定期間いっぱい（M12・M13）、亡くなった人に遺族厚生年金が無いケースの中高齢寡婦加算を0（N9・N15・N16）。金額が変わるのは GT-06 本人死亡だけ。</t>
+          <t>2026-09-23再構築（60dbe72追随・検算自体は8/23に人が実施済み）。教育費を段階別モデル（対応コミット 60dbe72・2026-08-23）に追随。GT-02・GT-06 の教育費／必要額／提示レンジを「教育費(段階別)」シートの式から引き直した。他8世帯は不変。 2026-10-17：遺族年金の受給要件を現行制度に合わせた（QA指摘）。GT-04 の遺族厚生年金を5年→算定期間いっぱい（M12・M13）、亡くなった人に遺族厚生年金が無いケースの中高齢寡婦加算を0（N9・N15・N16）。金額が変わるのは GT-06 本人死亡だけ。 2026-10-18：遺族の就労収入を60歳までに（ADR-030）。O列を「就労収入(60歳まで)」シートの式に置き換えた。必要額が変わるのは GT-02・GT-06 の本人死亡だけ（専業の遺族＝独立後の下限が60歳で止まる）。他は判定が ample／sufficient のまま提示額が変わらない。 同日、H列（教育費）を全行「教育費(段階別)」シートの式に揃えた（段階別化の前の値が8世帯に残っていた。金額が変わるのは GT-08 本人死亡の必要額の内訳だけで、提示額と判定は変わらない）。</t>
         </is>
       </c>
     </row>
@@ -842,8 +843,9 @@
       <c r="G6" s="34" t="n">
         <v>1800</v>
       </c>
-      <c r="H6" s="34" t="n">
-        <v>909</v>
+      <c r="H6" s="34">
+        <f>'教育費(段階別)'!D22</f>
+        <v/>
       </c>
       <c r="I6" s="34" t="n">
         <v>0</v>
@@ -864,8 +866,9 @@
       <c r="N6" s="34" t="n">
         <v>890</v>
       </c>
-      <c r="O6" s="34" t="n">
-        <v>6000</v>
+      <c r="O6" s="34">
+        <f>'就労収入(60歳まで)'!K7</f>
+        <v/>
       </c>
       <c r="P6" s="34" t="n">
         <v>400</v>
@@ -925,8 +928,9 @@
       <c r="G7" s="34" t="n">
         <v>1440</v>
       </c>
-      <c r="H7" s="34" t="n">
-        <v>909</v>
+      <c r="H7" s="34">
+        <f>'教育費(段階別)'!D22</f>
+        <v/>
       </c>
       <c r="I7" s="34" t="n">
         <v>0</v>
@@ -947,8 +951,9 @@
       <c r="N7" s="34" t="n">
         <v>763</v>
       </c>
-      <c r="O7" s="34" t="n">
-        <v>11200</v>
+      <c r="O7" s="34">
+        <f>'就労収入(60歳まで)'!K8</f>
+        <v/>
       </c>
       <c r="P7" s="34" t="n">
         <v>400</v>
@@ -1031,8 +1036,9 @@
       <c r="N8" s="34" t="n">
         <v>890</v>
       </c>
-      <c r="O8" s="34" t="n">
-        <v>1000</v>
+      <c r="O8" s="34">
+        <f>'就労収入(60歳まで)'!K9</f>
+        <v/>
       </c>
       <c r="P8" s="34" t="n">
         <v>200</v>
@@ -1094,8 +1100,9 @@
       <c r="G9" s="34" t="n">
         <v>1176</v>
       </c>
-      <c r="H9" s="34" t="n">
-        <v>1682</v>
+      <c r="H9" s="34">
+        <f>'教育費(段階別)'!D19</f>
+        <v/>
       </c>
       <c r="I9" s="34" t="n">
         <v>0</v>
@@ -1116,8 +1123,9 @@
       <c r="N9" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="34" t="n">
-        <v>10800</v>
+      <c r="O9" s="34">
+        <f>'就労収入(60歳まで)'!K10</f>
+        <v/>
       </c>
       <c r="P9" s="34" t="n">
         <v>200</v>
@@ -1177,8 +1185,9 @@
       <c r="G10" s="34" t="n">
         <v>2520</v>
       </c>
-      <c r="H10" s="34" t="n">
-        <v>1227</v>
+      <c r="H10" s="34">
+        <f>'教育費(段階別)'!D23</f>
+        <v/>
       </c>
       <c r="I10" s="34" t="n">
         <v>0</v>
@@ -1199,8 +1208,9 @@
       <c r="N10" s="34" t="n">
         <v>1017</v>
       </c>
-      <c r="O10" s="34" t="n">
-        <v>8640</v>
+      <c r="O10" s="34">
+        <f>'就労収入(60歳まで)'!K11</f>
+        <v/>
       </c>
       <c r="P10" s="34" t="n">
         <v>600</v>
@@ -1260,8 +1270,9 @@
       <c r="G11" s="34" t="n">
         <v>2100</v>
       </c>
-      <c r="H11" s="34" t="n">
-        <v>1227</v>
+      <c r="H11" s="34">
+        <f>'教育費(段階別)'!D23</f>
+        <v/>
       </c>
       <c r="I11" s="34" t="n">
         <v>0</v>
@@ -1282,8 +1293,9 @@
       <c r="N11" s="34" t="n">
         <v>890</v>
       </c>
-      <c r="O11" s="34" t="n">
-        <v>14000</v>
+      <c r="O11" s="34">
+        <f>'就労収入(60歳まで)'!K12</f>
+        <v/>
       </c>
       <c r="P11" s="34" t="n">
         <v>600</v>
@@ -1365,8 +1377,9 @@
       <c r="N12" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="34" t="n">
-        <v>11200</v>
+      <c r="O12" s="34">
+        <f>'就労収入(60歳まで)'!K13</f>
+        <v/>
       </c>
       <c r="P12" s="34" t="n">
         <v>300</v>
@@ -1448,8 +1461,9 @@
       <c r="N13" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="34" t="n">
-        <v>11880</v>
+      <c r="O13" s="34">
+        <f>'就労収入(60歳まで)'!K14</f>
+        <v/>
       </c>
       <c r="P13" s="34" t="n">
         <v>300</v>
@@ -1531,8 +1545,9 @@
       <c r="N14" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="34" t="n">
-        <v>0</v>
+      <c r="O14" s="34">
+        <f>'就労収入(60歳まで)'!K15</f>
+        <v/>
       </c>
       <c r="P14" s="34" t="n">
         <v>300</v>
@@ -1615,8 +1630,9 @@
       <c r="N15" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="34" t="n">
-        <v>1200</v>
+      <c r="O15" s="34">
+        <f>'就労収入(60歳まで)'!K16</f>
+        <v/>
       </c>
       <c r="P15" s="34" t="n">
         <v>500</v>
@@ -1678,8 +1694,9 @@
       <c r="G16" s="34" t="n">
         <v>1800</v>
       </c>
-      <c r="H16" s="34" t="n">
-        <v>455</v>
+      <c r="H16" s="34">
+        <f>'教育費(段階別)'!D20</f>
+        <v/>
       </c>
       <c r="I16" s="34" t="n">
         <v>0</v>
@@ -1700,8 +1717,9 @@
       <c r="N16" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="34" t="n">
-        <v>9600</v>
+      <c r="O16" s="34">
+        <f>'就労収入(60歳まで)'!K17</f>
+        <v/>
       </c>
       <c r="P16" s="34" t="n">
         <v>500</v>
@@ -1761,8 +1779,9 @@
       <c r="G17" s="34" t="n">
         <v>2736</v>
       </c>
-      <c r="H17" s="34" t="n">
-        <v>773</v>
+      <c r="H17" s="34">
+        <f>'教育費(段階別)'!D24</f>
+        <v/>
       </c>
       <c r="I17" s="34" t="n">
         <v>1500</v>
@@ -1783,8 +1802,9 @@
       <c r="N17" s="34" t="n">
         <v>1017</v>
       </c>
-      <c r="O17" s="34" t="n">
-        <v>5280</v>
+      <c r="O17" s="34">
+        <f>'就労収入(60歳まで)'!K18</f>
+        <v/>
       </c>
       <c r="P17" s="34" t="n">
         <v>800</v>
@@ -1844,8 +1864,9 @@
       <c r="G18" s="34" t="n">
         <v>2280</v>
       </c>
-      <c r="H18" s="34" t="n">
-        <v>773</v>
+      <c r="H18" s="34">
+        <f>'教育費(段階別)'!D24</f>
+        <v/>
       </c>
       <c r="I18" s="34" t="n">
         <v>1500</v>
@@ -1866,8 +1887,9 @@
       <c r="N18" s="34" t="n">
         <v>890</v>
       </c>
-      <c r="O18" s="34" t="n">
-        <v>12800</v>
+      <c r="O18" s="34">
+        <f>'就労収入(60歳まで)'!K19</f>
+        <v/>
       </c>
       <c r="P18" s="34" t="n">
         <v>800</v>
@@ -1927,8 +1949,9 @@
       <c r="G19" s="34" t="n">
         <v>1872</v>
       </c>
-      <c r="H19" s="34" t="n">
-        <v>864</v>
+      <c r="H19" s="34">
+        <f>'教育費(段階別)'!D25</f>
+        <v/>
       </c>
       <c r="I19" s="34" t="n">
         <v>0</v>
@@ -1949,8 +1972,9 @@
       <c r="N19" s="34" t="n">
         <v>1081</v>
       </c>
-      <c r="O19" s="34" t="n">
-        <v>2820</v>
+      <c r="O19" s="34">
+        <f>'就労収入(60歳まで)'!K20</f>
+        <v/>
       </c>
       <c r="P19" s="34" t="n">
         <v>100</v>
@@ -2010,8 +2034,9 @@
       <c r="G20" s="34" t="n">
         <v>1584</v>
       </c>
-      <c r="H20" s="34" t="n">
-        <v>864</v>
+      <c r="H20" s="34">
+        <f>'教育費(段階別)'!D25</f>
+        <v/>
       </c>
       <c r="I20" s="34" t="n">
         <v>0</v>
@@ -2032,8 +2057,9 @@
       <c r="N20" s="34" t="n">
         <v>954</v>
       </c>
-      <c r="O20" s="34" t="n">
-        <v>9600</v>
+      <c r="O20" s="34">
+        <f>'就労収入(60歳まで)'!K21</f>
+        <v/>
       </c>
       <c r="P20" s="34" t="n">
         <v>100</v>
@@ -2093,8 +2119,9 @@
       <c r="G21" s="34" t="n">
         <v>3600</v>
       </c>
-      <c r="H21" s="34" t="n">
-        <v>182</v>
+      <c r="H21" s="34">
+        <f>'教育費(段階別)'!D26</f>
+        <v/>
       </c>
       <c r="I21" s="34" t="n">
         <v>0</v>
@@ -2115,8 +2142,9 @@
       <c r="N21" s="34" t="n">
         <v>1081</v>
       </c>
-      <c r="O21" s="34" t="n">
-        <v>8160</v>
+      <c r="O21" s="34">
+        <f>'就労収入(60歳まで)'!K22</f>
+        <v/>
       </c>
       <c r="P21" s="34" t="n">
         <v>2000</v>
@@ -2176,8 +2204,9 @@
       <c r="G22" s="34" t="n">
         <v>3120</v>
       </c>
-      <c r="H22" s="34" t="n">
-        <v>182</v>
+      <c r="H22" s="34">
+        <f>'教育費(段階別)'!D26</f>
+        <v/>
       </c>
       <c r="I22" s="34" t="n">
         <v>0</v>
@@ -2198,8 +2227,9 @@
       <c r="N22" s="34" t="n">
         <v>954</v>
       </c>
-      <c r="O22" s="34" t="n">
-        <v>14400</v>
+      <c r="O22" s="34">
+        <f>'就労収入(60歳まで)'!K23</f>
+        <v/>
       </c>
       <c r="P22" s="34" t="n">
         <v>2000</v>
@@ -2259,8 +2289,9 @@
       <c r="G23" s="34" t="n">
         <v>2496</v>
       </c>
-      <c r="H23" s="34" t="n">
-        <v>727</v>
+      <c r="H23" s="34">
+        <f>'教育費(段階別)'!D27</f>
+        <v/>
       </c>
       <c r="I23" s="34" t="n">
         <v>0</v>
@@ -2281,8 +2312,9 @@
       <c r="N23" s="34" t="n">
         <v>1081</v>
       </c>
-      <c r="O23" s="34" t="n">
-        <v>16240</v>
+      <c r="O23" s="34">
+        <f>'就労収入(60歳まで)'!K24</f>
+        <v/>
       </c>
       <c r="P23" s="34" t="n">
         <v>400</v>
@@ -2342,8 +2374,9 @@
       <c r="G24" s="34" t="n">
         <v>2112</v>
       </c>
-      <c r="H24" s="34" t="n">
-        <v>727</v>
+      <c r="H24" s="34">
+        <f>'教育費(段階別)'!D27</f>
+        <v/>
       </c>
       <c r="I24" s="34" t="n">
         <v>0</v>
@@ -2364,8 +2397,9 @@
       <c r="N24" s="34" t="n">
         <v>954</v>
       </c>
-      <c r="O24" s="34" t="n">
-        <v>6480</v>
+      <c r="O24" s="34">
+        <f>'就労収入(60歳まで)'!K25</f>
+        <v/>
       </c>
       <c r="P24" s="34" t="n">
         <v>400</v>
@@ -2414,7 +2448,7 @@
     <row r="28" ht="15" customHeight="1" s="27">
       <c r="A28" s="39" t="inlineStr">
         <is>
-          <t>・遺族の就労収入は、子育て期＝現在の手取り（年収×80%）、末子独立後＝現在の手取りとパート相当100万円の大きい方で連続推定（grill Q3-b：分岐の崖をなくす）。</t>
+          <t>・遺族の就労収入は、子育て期＝現在の手取り（年収×80%）、末子独立後＝現在の手取りとパート相当100万円の大きい方で連続推定（grill Q3-b：分岐の崖をなくす）。見込むのは遺族が60歳になるまで（2026-10-18・ADR-030。職種を問わない当社基準。すでに60歳以上なら、いまの手取りを65歳まで）。</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4061,6 +4095,1187 @@
         <v/>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-18 追加：他の世帯も同じ式で引き直した（それまで「テスト結果」H列に段階別化の前の値が残っていた。GT-02・GT-06 の配偶者死亡の行も同じ）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GT-01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2歳</t>
+        </is>
+      </c>
+      <c r="C22">
+        <f>SUM(D$16:W$16)</f>
+        <v/>
+      </c>
+      <c r="D22">
+        <f>ROUND(C22/10000,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>GT-03</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>10歳・7歳</t>
+        </is>
+      </c>
+      <c r="C23">
+        <f>SUM(L$16:W$16)+SUM(I$16:W$16)</f>
+        <v/>
+      </c>
+      <c r="D23">
+        <f>ROUND(C23/10000,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>GT-07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>15歳・12歳</t>
+        </is>
+      </c>
+      <c r="C24">
+        <f>SUM(Q$16:W$16)+SUM(N$16:W$16)</f>
+        <v/>
+      </c>
+      <c r="D24">
+        <f>ROUND(C24/10000,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GT-08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>3歳</t>
+        </is>
+      </c>
+      <c r="C25">
+        <f>SUM(E$16:W$16)</f>
+        <v/>
+      </c>
+      <c r="D25">
+        <f>ROUND(C25/10000,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>GT-09</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>20歳（私立中心＝大学は私立理系）</t>
+        </is>
+      </c>
+      <c r="C26">
+        <f>2*$E$10</f>
+        <v/>
+      </c>
+      <c r="D26">
+        <f>ROUND(C26/10000,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>GT-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>6歳</t>
+        </is>
+      </c>
+      <c r="C27">
+        <f>SUM(H$16:W$16)</f>
+        <v/>
+      </c>
+      <c r="D27">
+        <f>ROUND(C27/10000,0)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>遺族の就労収入（60歳まで）の検算 ─ ADR-030 / params.ownStandard.survivorWorkEndAge / src/calc/work.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-18 追加。就労収入を見込むのは遺族が60歳になる年の前年まで（職種を問わない・当社基準）。生活費・遺族年金の算定期間（65歳まで）は変えない。すでに60歳以上なら、いまの手取りを65歳まで（下限なし）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>単位：万円。手取り＝年収×手取り率。独立後＝手取りと下限（年100万円）の大きい方。年数は「テスト結果」シートの子育て年数・独立後年数を参照。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>終わりの年齢</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="n">
+        <v>60</v>
+      </c>
+      <c r="D4" s="26" t="inlineStr">
+        <is>
+          <t>手取り率</t>
+        </is>
+      </c>
+      <c r="E4" s="26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F4" s="26" t="inlineStr">
+        <is>
+          <t>独立後の下限</t>
+        </is>
+      </c>
+      <c r="G4" s="26" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>死亡ケース</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>遺族の年齢</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>遺族の年収</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>子育て年数</t>
+        </is>
+      </c>
+      <c r="F6" s="26" t="inlineStr">
+        <is>
+          <t>独立後年数</t>
+        </is>
+      </c>
+      <c r="G6" s="26" t="inlineStr">
+        <is>
+          <t>手取り(年)</t>
+        </is>
+      </c>
+      <c r="H6" s="26" t="inlineStr">
+        <is>
+          <t>独立後(年)</t>
+        </is>
+      </c>
+      <c r="I6" s="26" t="inlineStr">
+        <is>
+          <t>就労を入れる子育て年数</t>
+        </is>
+      </c>
+      <c r="J6" s="26" t="inlineStr">
+        <is>
+          <t>就労を入れる独立後年数</t>
+        </is>
+      </c>
+      <c r="K6" s="26" t="inlineStr">
+        <is>
+          <t>遺族の就労収入</t>
+        </is>
+      </c>
+      <c r="L6" s="26" t="inlineStr">
+        <is>
+          <t>変更前（65歳まで）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>GT-01</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>本人死亡</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="n">
+        <v>35</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>250</v>
+      </c>
+      <c r="E7" s="26">
+        <f>'テスト結果'!D6</f>
+        <v/>
+      </c>
+      <c r="F7" s="26">
+        <f>'テスト結果'!E6</f>
+        <v/>
+      </c>
+      <c r="G7" s="26">
+        <f>D7*$E$4</f>
+        <v/>
+      </c>
+      <c r="H7" s="26">
+        <f>IF(C7&gt;=$C$4,G7,MAX(G7,$G$4))</f>
+        <v/>
+      </c>
+      <c r="I7" s="26">
+        <f>IF(C7&gt;=$C$4,E7,MIN(E7,MAX(0,$C$4-C7)))</f>
+        <v/>
+      </c>
+      <c r="J7" s="26">
+        <f>IF(C7&gt;=$C$4,F7,MAX(0,MIN(E7+F7,MAX(0,$C$4-C7))-I7))</f>
+        <v/>
+      </c>
+      <c r="K7" s="26">
+        <f>ROUND(G7*I7+H7*J7,0)</f>
+        <v/>
+      </c>
+      <c r="L7" s="26" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>GT-01</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>配偶者死亡</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="n">
+        <v>37</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>500</v>
+      </c>
+      <c r="E8" s="26">
+        <f>'テスト結果'!D7</f>
+        <v/>
+      </c>
+      <c r="F8" s="26">
+        <f>'テスト結果'!E7</f>
+        <v/>
+      </c>
+      <c r="G8" s="26">
+        <f>D8*$E$4</f>
+        <v/>
+      </c>
+      <c r="H8" s="26">
+        <f>IF(C8&gt;=$C$4,G8,MAX(G8,$G$4))</f>
+        <v/>
+      </c>
+      <c r="I8" s="26">
+        <f>IF(C8&gt;=$C$4,E8,MIN(E8,MAX(0,$C$4-C8)))</f>
+        <v/>
+      </c>
+      <c r="J8" s="26">
+        <f>IF(C8&gt;=$C$4,F8,MAX(0,MIN(E8+F8,MAX(0,$C$4-C8))-I8))</f>
+        <v/>
+      </c>
+      <c r="K8" s="26">
+        <f>ROUND(G8*I8+H8*J8,0)</f>
+        <v/>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>11200</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>GT-02</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>本人死亡</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="n">
+        <v>35</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="26">
+        <f>'テスト結果'!D8</f>
+        <v/>
+      </c>
+      <c r="F9" s="26">
+        <f>'テスト結果'!E8</f>
+        <v/>
+      </c>
+      <c r="G9" s="26">
+        <f>D9*$E$4</f>
+        <v/>
+      </c>
+      <c r="H9" s="26">
+        <f>IF(C9&gt;=$C$4,G9,MAX(G9,$G$4))</f>
+        <v/>
+      </c>
+      <c r="I9" s="26">
+        <f>IF(C9&gt;=$C$4,E9,MIN(E9,MAX(0,$C$4-C9)))</f>
+        <v/>
+      </c>
+      <c r="J9" s="26">
+        <f>IF(C9&gt;=$C$4,F9,MAX(0,MIN(E9+F9,MAX(0,$C$4-C9))-I9))</f>
+        <v/>
+      </c>
+      <c r="K9" s="26">
+        <f>ROUND(G9*I9+H9*J9,0)</f>
+        <v/>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>GT-02</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>配偶者死亡</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>500</v>
+      </c>
+      <c r="E10" s="26">
+        <f>'テスト結果'!D9</f>
+        <v/>
+      </c>
+      <c r="F10" s="26">
+        <f>'テスト結果'!E9</f>
+        <v/>
+      </c>
+      <c r="G10" s="26">
+        <f>D10*$E$4</f>
+        <v/>
+      </c>
+      <c r="H10" s="26">
+        <f>IF(C10&gt;=$C$4,G10,MAX(G10,$G$4))</f>
+        <v/>
+      </c>
+      <c r="I10" s="26">
+        <f>IF(C10&gt;=$C$4,E10,MIN(E10,MAX(0,$C$4-C10)))</f>
+        <v/>
+      </c>
+      <c r="J10" s="26">
+        <f>IF(C10&gt;=$C$4,F10,MAX(0,MIN(E10+F10,MAX(0,$C$4-C10))-I10))</f>
+        <v/>
+      </c>
+      <c r="K10" s="26">
+        <f>ROUND(G10*I10+H10*J10,0)</f>
+        <v/>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>GT-03</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>本人死亡</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>400</v>
+      </c>
+      <c r="E11" s="26">
+        <f>'テスト結果'!D10</f>
+        <v/>
+      </c>
+      <c r="F11" s="26">
+        <f>'テスト結果'!E10</f>
+        <v/>
+      </c>
+      <c r="G11" s="26">
+        <f>D11*$E$4</f>
+        <v/>
+      </c>
+      <c r="H11" s="26">
+        <f>IF(C11&gt;=$C$4,G11,MAX(G11,$G$4))</f>
+        <v/>
+      </c>
+      <c r="I11" s="26">
+        <f>IF(C11&gt;=$C$4,E11,MIN(E11,MAX(0,$C$4-C11)))</f>
+        <v/>
+      </c>
+      <c r="J11" s="26">
+        <f>IF(C11&gt;=$C$4,F11,MAX(0,MIN(E11+F11,MAX(0,$C$4-C11))-I11))</f>
+        <v/>
+      </c>
+      <c r="K11" s="26">
+        <f>ROUND(G11*I11+H11*J11,0)</f>
+        <v/>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>GT-03</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>配偶者死亡</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="n">
+        <v>40</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>700</v>
+      </c>
+      <c r="E12" s="26">
+        <f>'テスト結果'!D11</f>
+        <v/>
+      </c>
+      <c r="F12" s="26">
+        <f>'テスト結果'!E11</f>
+        <v/>
+      </c>
+      <c r="G12" s="26">
+        <f>D12*$E$4</f>
+        <v/>
+      </c>
+      <c r="H12" s="26">
+        <f>IF(C12&gt;=$C$4,G12,MAX(G12,$G$4))</f>
+        <v/>
+      </c>
+      <c r="I12" s="26">
+        <f>IF(C12&gt;=$C$4,E12,MIN(E12,MAX(0,$C$4-C12)))</f>
+        <v/>
+      </c>
+      <c r="J12" s="26">
+        <f>IF(C12&gt;=$C$4,F12,MAX(0,MIN(E12+F12,MAX(0,$C$4-C12))-I12))</f>
+        <v/>
+      </c>
+      <c r="K12" s="26">
+        <f>ROUND(G12*I12+H12*J12,0)</f>
+        <v/>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>GT-04</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>本人死亡</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>400</v>
+      </c>
+      <c r="E13" s="26">
+        <f>'テスト結果'!D12</f>
+        <v/>
+      </c>
+      <c r="F13" s="26">
+        <f>'テスト結果'!E12</f>
+        <v/>
+      </c>
+      <c r="G13" s="26">
+        <f>D13*$E$4</f>
+        <v/>
+      </c>
+      <c r="H13" s="26">
+        <f>IF(C13&gt;=$C$4,G13,MAX(G13,$G$4))</f>
+        <v/>
+      </c>
+      <c r="I13" s="26">
+        <f>IF(C13&gt;=$C$4,E13,MIN(E13,MAX(0,$C$4-C13)))</f>
+        <v/>
+      </c>
+      <c r="J13" s="26">
+        <f>IF(C13&gt;=$C$4,F13,MAX(0,MIN(E13+F13,MAX(0,$C$4-C13))-I13))</f>
+        <v/>
+      </c>
+      <c r="K13" s="26">
+        <f>ROUND(G13*I13+H13*J13,0)</f>
+        <v/>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>11200</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>GT-04</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>配偶者死亡</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="n">
+        <v>32</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>450</v>
+      </c>
+      <c r="E14" s="26">
+        <f>'テスト結果'!D13</f>
+        <v/>
+      </c>
+      <c r="F14" s="26">
+        <f>'テスト結果'!E13</f>
+        <v/>
+      </c>
+      <c r="G14" s="26">
+        <f>D14*$E$4</f>
+        <v/>
+      </c>
+      <c r="H14" s="26">
+        <f>IF(C14&gt;=$C$4,G14,MAX(G14,$G$4))</f>
+        <v/>
+      </c>
+      <c r="I14" s="26">
+        <f>IF(C14&gt;=$C$4,E14,MIN(E14,MAX(0,$C$4-C14)))</f>
+        <v/>
+      </c>
+      <c r="J14" s="26">
+        <f>IF(C14&gt;=$C$4,F14,MAX(0,MIN(E14+F14,MAX(0,$C$4-C14))-I14))</f>
+        <v/>
+      </c>
+      <c r="K14" s="26">
+        <f>ROUND(G14*I14+H14*J14,0)</f>
+        <v/>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>11880</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>GT-05</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>本人死亡</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>GT-06</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>本人死亡</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="n">
+        <v>43</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="26">
+        <f>'テスト結果'!D15</f>
+        <v/>
+      </c>
+      <c r="F16" s="26">
+        <f>'テスト結果'!E15</f>
+        <v/>
+      </c>
+      <c r="G16" s="26">
+        <f>D16*$E$4</f>
+        <v/>
+      </c>
+      <c r="H16" s="26">
+        <f>IF(C16&gt;=$C$4,G16,MAX(G16,$G$4))</f>
+        <v/>
+      </c>
+      <c r="I16" s="26">
+        <f>IF(C16&gt;=$C$4,E16,MIN(E16,MAX(0,$C$4-C16)))</f>
+        <v/>
+      </c>
+      <c r="J16" s="26">
+        <f>IF(C16&gt;=$C$4,F16,MAX(0,MIN(E16+F16,MAX(0,$C$4-C16))-I16))</f>
+        <v/>
+      </c>
+      <c r="K16" s="26">
+        <f>ROUND(G16*I16+H16*J16,0)</f>
+        <v/>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>GT-06</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>配偶者死亡</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>600</v>
+      </c>
+      <c r="E17" s="26">
+        <f>'テスト結果'!D16</f>
+        <v/>
+      </c>
+      <c r="F17" s="26">
+        <f>'テスト結果'!E16</f>
+        <v/>
+      </c>
+      <c r="G17" s="26">
+        <f>D17*$E$4</f>
+        <v/>
+      </c>
+      <c r="H17" s="26">
+        <f>IF(C17&gt;=$C$4,G17,MAX(G17,$G$4))</f>
+        <v/>
+      </c>
+      <c r="I17" s="26">
+        <f>IF(C17&gt;=$C$4,E17,MIN(E17,MAX(0,$C$4-C17)))</f>
+        <v/>
+      </c>
+      <c r="J17" s="26">
+        <f>IF(C17&gt;=$C$4,F17,MAX(0,MIN(E17+F17,MAX(0,$C$4-C17))-I17))</f>
+        <v/>
+      </c>
+      <c r="K17" s="26">
+        <f>ROUND(G17*I17+H17*J17,0)</f>
+        <v/>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>GT-07</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>本人死亡</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="n">
+        <v>43</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="E18" s="26">
+        <f>'テスト結果'!D17</f>
+        <v/>
+      </c>
+      <c r="F18" s="26">
+        <f>'テスト結果'!E17</f>
+        <v/>
+      </c>
+      <c r="G18" s="26">
+        <f>D18*$E$4</f>
+        <v/>
+      </c>
+      <c r="H18" s="26">
+        <f>IF(C18&gt;=$C$4,G18,MAX(G18,$G$4))</f>
+        <v/>
+      </c>
+      <c r="I18" s="26">
+        <f>IF(C18&gt;=$C$4,E18,MIN(E18,MAX(0,$C$4-C18)))</f>
+        <v/>
+      </c>
+      <c r="J18" s="26">
+        <f>IF(C18&gt;=$C$4,F18,MAX(0,MIN(E18+F18,MAX(0,$C$4-C18))-I18))</f>
+        <v/>
+      </c>
+      <c r="K18" s="26">
+        <f>ROUND(G18*I18+H18*J18,0)</f>
+        <v/>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>5280</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>GT-07</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>配偶者死亡</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>800</v>
+      </c>
+      <c r="E19" s="26">
+        <f>'テスト結果'!D18</f>
+        <v/>
+      </c>
+      <c r="F19" s="26">
+        <f>'テスト結果'!E18</f>
+        <v/>
+      </c>
+      <c r="G19" s="26">
+        <f>D19*$E$4</f>
+        <v/>
+      </c>
+      <c r="H19" s="26">
+        <f>IF(C19&gt;=$C$4,G19,MAX(G19,$G$4))</f>
+        <v/>
+      </c>
+      <c r="I19" s="26">
+        <f>IF(C19&gt;=$C$4,E19,MIN(E19,MAX(0,$C$4-C19)))</f>
+        <v/>
+      </c>
+      <c r="J19" s="26">
+        <f>IF(C19&gt;=$C$4,F19,MAX(0,MIN(E19+F19,MAX(0,$C$4-C19))-I19))</f>
+        <v/>
+      </c>
+      <c r="K19" s="26">
+        <f>ROUND(G19*I19+H19*J19,0)</f>
+        <v/>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>12800</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>GT-08</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>本人死亡</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="n">
+        <v>33</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" s="26">
+        <f>'テスト結果'!D19</f>
+        <v/>
+      </c>
+      <c r="F20" s="26">
+        <f>'テスト結果'!E19</f>
+        <v/>
+      </c>
+      <c r="G20" s="26">
+        <f>D20*$E$4</f>
+        <v/>
+      </c>
+      <c r="H20" s="26">
+        <f>IF(C20&gt;=$C$4,G20,MAX(G20,$G$4))</f>
+        <v/>
+      </c>
+      <c r="I20" s="26">
+        <f>IF(C20&gt;=$C$4,E20,MIN(E20,MAX(0,$C$4-C20)))</f>
+        <v/>
+      </c>
+      <c r="J20" s="26">
+        <f>IF(C20&gt;=$C$4,F20,MAX(0,MIN(E20+F20,MAX(0,$C$4-C20))-I20))</f>
+        <v/>
+      </c>
+      <c r="K20" s="26">
+        <f>ROUND(G20*I20+H20*J20,0)</f>
+        <v/>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>2820</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>GT-08</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>配偶者死亡</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="n">
+        <v>35</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>400</v>
+      </c>
+      <c r="E21" s="26">
+        <f>'テスト結果'!D20</f>
+        <v/>
+      </c>
+      <c r="F21" s="26">
+        <f>'テスト結果'!E20</f>
+        <v/>
+      </c>
+      <c r="G21" s="26">
+        <f>D21*$E$4</f>
+        <v/>
+      </c>
+      <c r="H21" s="26">
+        <f>IF(C21&gt;=$C$4,G21,MAX(G21,$G$4))</f>
+        <v/>
+      </c>
+      <c r="I21" s="26">
+        <f>IF(C21&gt;=$C$4,E21,MIN(E21,MAX(0,$C$4-C21)))</f>
+        <v/>
+      </c>
+      <c r="J21" s="26">
+        <f>IF(C21&gt;=$C$4,F21,MAX(0,MIN(E21+F21,MAX(0,$C$4-C21))-I21))</f>
+        <v/>
+      </c>
+      <c r="K21" s="26">
+        <f>ROUND(G21*I21+H21*J21,0)</f>
+        <v/>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>GT-09</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>本人死亡</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="n">
+        <v>48</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>600</v>
+      </c>
+      <c r="E22" s="26">
+        <f>'テスト結果'!D21</f>
+        <v/>
+      </c>
+      <c r="F22" s="26">
+        <f>'テスト結果'!E21</f>
+        <v/>
+      </c>
+      <c r="G22" s="26">
+        <f>D22*$E$4</f>
+        <v/>
+      </c>
+      <c r="H22" s="26">
+        <f>IF(C22&gt;=$C$4,G22,MAX(G22,$G$4))</f>
+        <v/>
+      </c>
+      <c r="I22" s="26">
+        <f>IF(C22&gt;=$C$4,E22,MIN(E22,MAX(0,$C$4-C22)))</f>
+        <v/>
+      </c>
+      <c r="J22" s="26">
+        <f>IF(C22&gt;=$C$4,F22,MAX(0,MIN(E22+F22,MAX(0,$C$4-C22))-I22))</f>
+        <v/>
+      </c>
+      <c r="K22" s="26">
+        <f>ROUND(G22*I22+H22*J22,0)</f>
+        <v/>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>8160</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>GT-09</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>配偶者死亡</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E23" s="26">
+        <f>'テスト結果'!D22</f>
+        <v/>
+      </c>
+      <c r="F23" s="26">
+        <f>'テスト結果'!E22</f>
+        <v/>
+      </c>
+      <c r="G23" s="26">
+        <f>D23*$E$4</f>
+        <v/>
+      </c>
+      <c r="H23" s="26">
+        <f>IF(C23&gt;=$C$4,G23,MAX(G23,$G$4))</f>
+        <v/>
+      </c>
+      <c r="I23" s="26">
+        <f>IF(C23&gt;=$C$4,E23,MIN(E23,MAX(0,$C$4-C23)))</f>
+        <v/>
+      </c>
+      <c r="J23" s="26">
+        <f>IF(C23&gt;=$C$4,F23,MAX(0,MIN(E23+F23,MAX(0,$C$4-C23))-I23))</f>
+        <v/>
+      </c>
+      <c r="K23" s="26">
+        <f>ROUND(G23*I23+H23*J23,0)</f>
+        <v/>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>GT-10</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>本人死亡</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="n">
+        <v>36</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>700</v>
+      </c>
+      <c r="E24" s="26">
+        <f>'テスト結果'!D23</f>
+        <v/>
+      </c>
+      <c r="F24" s="26">
+        <f>'テスト結果'!E23</f>
+        <v/>
+      </c>
+      <c r="G24" s="26">
+        <f>D24*$E$4</f>
+        <v/>
+      </c>
+      <c r="H24" s="26">
+        <f>IF(C24&gt;=$C$4,G24,MAX(G24,$G$4))</f>
+        <v/>
+      </c>
+      <c r="I24" s="26">
+        <f>IF(C24&gt;=$C$4,E24,MIN(E24,MAX(0,$C$4-C24)))</f>
+        <v/>
+      </c>
+      <c r="J24" s="26">
+        <f>IF(C24&gt;=$C$4,F24,MAX(0,MIN(E24+F24,MAX(0,$C$4-C24))-I24))</f>
+        <v/>
+      </c>
+      <c r="K24" s="26">
+        <f>ROUND(G24*I24+H24*J24,0)</f>
+        <v/>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>16240</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>GT-10</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>配偶者死亡</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="E25" s="26">
+        <f>'テスト結果'!D24</f>
+        <v/>
+      </c>
+      <c r="F25" s="26">
+        <f>'テスト結果'!E24</f>
+        <v/>
+      </c>
+      <c r="G25" s="26">
+        <f>D25*$E$4</f>
+        <v/>
+      </c>
+      <c r="H25" s="26">
+        <f>IF(C25&gt;=$C$4,G25,MAX(G25,$G$4))</f>
+        <v/>
+      </c>
+      <c r="I25" s="26">
+        <f>IF(C25&gt;=$C$4,E25,MIN(E25,MAX(0,$C$4-C25)))</f>
+        <v/>
+      </c>
+      <c r="J25" s="26">
+        <f>IF(C25&gt;=$C$4,F25,MAX(0,MIN(E25+F25,MAX(0,$C$4-C25))-I25))</f>
+        <v/>
+      </c>
+      <c r="K25" s="26">
+        <f>ROUND(G25*I25+H25*J25,0)</f>
+        <v/>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>6480</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>変更前（65歳まで）は 2026-10-18 以前に「テスト結果」O列にあった値（参照用に残す）。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
